--- a/public/downloads/PengRole2020.xlsx
+++ b/public/downloads/PengRole2020.xlsx
@@ -1536,16 +1536,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5588717714072137</v>
+        <v>-0.5738930100077866</v>
       </c>
       <c r="O3" s="5">
         <v>57</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4429582655182749</v>
+        <v>0.4436653871599675</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1054788592382046</v>
+        <v>0.1039360064859121</v>
       </c>
       <c r="R3" s="5">
         <v>56</v>
@@ -1595,16 +1595,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.052071383310881</v>
+        <v>-1.03923159368042</v>
       </c>
       <c r="O4" s="5">
         <v>41</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1742174489580337</v>
+        <v>0.1745160487168817</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1606732616270575</v>
+        <v>0.1603600960263145</v>
       </c>
       <c r="R4" s="5">
         <v>41</v>
@@ -1654,13 +1654,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2889581718292651</v>
+        <v>-0.2823156221756591</v>
       </c>
       <c r="O5" s="5">
         <v>14</v>
       </c>
       <c r="P5" s="4">
-        <v>0.05260065086513176</v>
+        <v>0.05215781422155803</v>
       </c>
       <c r="Q5" s="4">
         <v>0.05474378581653795</v>
@@ -1713,16 +1713,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.9301394370724095</v>
+        <v>-1.422934124853271</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
       </c>
       <c r="P6" s="4">
-        <v>0.9927593143850371</v>
+        <v>0.7494910284452537</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.5956555886310222</v>
+        <v>0.2051747079471099</v>
       </c>
       <c r="R6" s="5">
         <v>10</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.25420190522878</v>
+        <v>-1.285962766195591</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1294715064610009</v>
+        <v>0.1273860050524493</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1294715064610009</v>
+        <v>0.1273860050524493</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -1831,16 +1831,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.276368083022837</v>
+        <v>-1.295301626011832</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.0675942062957724</v>
+        <v>0.06030402906809007</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.0675942062957724</v>
+        <v>0.06030402906809007</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -2461,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2349316383383519</v>
+        <v>-0.3847929869352811</v>
       </c>
       <c r="O3" s="5">
         <v>62</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4880796198217258</v>
+        <v>0.4542067399785689</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4835509738204469</v>
+        <v>0.4531050921529142</v>
       </c>
       <c r="R3" s="5">
         <v>62</v>
@@ -2520,16 +2520,16 @@
         <v>5</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.470713462843402</v>
+        <v>-1.464785894946544</v>
       </c>
       <c r="O4" s="5">
         <v>37</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4438460112799948</v>
+        <v>0.4431567591989649</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3689775486844014</v>
+        <v>0.3688173441466485</v>
       </c>
       <c r="R4" s="5">
         <v>37</v>
@@ -2579,13 +2579,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3706400533109055</v>
+        <v>-0.3749274331566994</v>
       </c>
       <c r="O5" s="5">
         <v>14</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1295681691257327</v>
+        <v>0.1298539944487857</v>
       </c>
       <c r="Q5" s="4">
         <v>0.1321112157872579</v>
@@ -2638,16 +2638,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.449340676259857</v>
+        <v>-1.732814312454138</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.4869284347059875</v>
+        <v>0.4920667775325758</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.5601640056883759</v>
+        <v>0.5286669350001224</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -2697,16 +2697,16 @@
         <v>5</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.668614741730077</v>
+        <v>-1.635565486896667</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4686117989610162</v>
+        <v>0.4686117989610163</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4686117989610162</v>
+        <v>0.4686117989610163</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -2756,13 +2756,13 @@
         <v>3</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.864714543871135</v>
+        <v>-1.898188887527795</v>
       </c>
       <c r="O8" s="5">
         <v>6</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3682047790440872</v>
+        <v>0.3598361931299223</v>
       </c>
       <c r="Q8" s="4">
         <v>0.410756851832654</v>
@@ -3374,16 +3374,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1364968566341782</v>
+        <v>-0.1676993461135341</v>
       </c>
       <c r="O3" s="5">
         <v>68</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1703375965860399</v>
+        <v>0.1672265696526447</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.162522142689784</v>
+        <v>0.1598242254997118</v>
       </c>
       <c r="R3" s="5">
         <v>68</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5187857567340515</v>
+        <v>-0.6203835299087892</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2781321864279662</v>
+        <v>0.2685620674460438</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2781321864279662</v>
+        <v>0.2685620674460438</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -3492,13 +3492,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1945956229930549</v>
+        <v>-0.195651670272784</v>
       </c>
       <c r="O5" s="5">
         <v>14</v>
       </c>
       <c r="P5" s="4">
-        <v>0.0873715761585326</v>
+        <v>0.08744197931051455</v>
       </c>
       <c r="Q5" s="4">
         <v>0.08582038704904298</v>
@@ -3551,16 +3551,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6720935158747161</v>
+        <v>-0.764310395080495</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2023861494138391</v>
+        <v>0.1850841211922264</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2023861494138391</v>
+        <v>0.1850841211922264</v>
       </c>
       <c r="R6" s="5">
         <v>12</v>
@@ -3610,16 +3610,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.5774197263025017</v>
+        <v>-0.6795889344523278</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3427110127168277</v>
+        <v>0.3035846689478955</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.3427110127168277</v>
+        <v>0.3035846689478955</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.6393371052987256</v>
+        <v>-0.7074228672565024</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1653607604345675</v>
+        <v>0.1472188730391792</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1653607604345675</v>
+        <v>0.1472188730391792</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -4307,16 +4307,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2650946502578033</v>
+        <v>-0.07954379784860066</v>
       </c>
       <c r="O3" s="5">
         <v>60</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9855033234109989</v>
+        <v>0.8510333660416781</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.356100893416373</v>
+        <v>0.1307655488016563</v>
       </c>
       <c r="R3" s="5">
         <v>58</v>
@@ -4366,16 +4366,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7993150720158578</v>
+        <v>-0.8305031869676895</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1691513882382101</v>
+        <v>0.1670067609089148</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1691513882382101</v>
+        <v>0.1670067609089148</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -4425,16 +4425,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4249992836853683</v>
+        <v>-0.3547280315251555</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1436117501188872</v>
+        <v>0.1348206073399827</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1436117501188872</v>
+        <v>0.1348206073399827</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -4484,16 +4484,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5257525230507863</v>
+        <v>-0.7080795533838682</v>
       </c>
       <c r="O6" s="5">
         <v>11</v>
       </c>
       <c r="P6" s="4">
-        <v>0.4191288146500455</v>
+        <v>0.3967366168817534</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2991850231008071</v>
+        <v>0.2581819864142083</v>
       </c>
       <c r="R6" s="5">
         <v>11</v>
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.055050647822403</v>
+        <v>-1.069818592022784</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
@@ -4602,16 +4602,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.202144889301962</v>
+        <v>-1.152891507259483</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1224714356792447</v>
+        <v>0.1110791980709109</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1224714356792447</v>
+        <v>0.1110791980709109</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -5236,16 +5236,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5399559619590296</v>
+        <v>-0.5054662784204993</v>
       </c>
       <c r="O3" s="5">
         <v>56</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5406466633142779</v>
+        <v>0.534440489072923</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1448309797031248</v>
+        <v>0.1427270712958619</v>
       </c>
       <c r="R3" s="5">
         <v>56</v>
@@ -5295,16 +5295,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.034392618322315</v>
+        <v>-1.004442988854862</v>
       </c>
       <c r="O4" s="5">
         <v>42</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1385758204662028</v>
+        <v>0.1376724651896058</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1305839894347279</v>
+        <v>0.1289460392832726</v>
       </c>
       <c r="R4" s="5">
         <v>42</v>
@@ -5354,16 +5354,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4232074885905604</v>
+        <v>-0.4219415668339934</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.05532181430530425</v>
+        <v>0.05523741952153311</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.05532181430530425</v>
+        <v>0.05523741952153311</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -5413,16 +5413,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6525549675087942</v>
+        <v>-1.465314928980661</v>
       </c>
       <c r="O6" s="5">
         <v>11</v>
       </c>
       <c r="P6" s="4">
-        <v>2.013916148688981</v>
+        <v>1.583939172017684</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.7976711876649377</v>
+        <v>0.1191468233650085</v>
       </c>
       <c r="R6" s="5">
         <v>10</v>
@@ -5472,16 +5472,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.269352551864965</v>
+        <v>-1.337986999194982</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1423306038009792</v>
+        <v>0.1368734538082208</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1423306038009792</v>
+        <v>0.1368734538082208</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -5531,16 +5531,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.354423789448447</v>
+        <v>-1.399452410081722</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1051007150510941</v>
+        <v>0.09539791519910068</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1051007150510941</v>
+        <v>0.09539791519910068</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -6165,16 +6165,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.004401893733463989</v>
+        <v>-0.009355886417344195</v>
       </c>
       <c r="O3" s="5">
         <v>68</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06828527419491226</v>
+        <v>0.06655727852136523</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06083695819655516</v>
+        <v>0.05928587111826195</v>
       </c>
       <c r="R3" s="5">
         <v>68</v>
@@ -6224,16 +6224,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2723096549816555</v>
+        <v>-0.2757041522927413</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1209281006950468</v>
+        <v>0.1208491588971146</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1209281006950468</v>
+        <v>0.1208491588971146</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -6283,16 +6283,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1075402527392719</v>
+        <v>-0.09180523757824277</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.03437084672079737</v>
+        <v>0.03241939504951006</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.03437084672079737</v>
+        <v>0.03241939504951006</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -6342,16 +6342,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.2038125602430321</v>
+        <v>-0.2080684142784248</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
       </c>
       <c r="P6" s="4">
-        <v>0.03580455302928409</v>
+        <v>0.03518788581460427</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.03580455302928409</v>
+        <v>0.03518788581460427</v>
       </c>
       <c r="R6" s="5">
         <v>12</v>
@@ -6401,16 +6401,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3365591034962632</v>
+        <v>-0.29898105958274</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.07534781000019398</v>
+        <v>0.07146765277745375</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.07534781000019398</v>
+        <v>0.07146765277745375</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -6460,16 +6460,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2170710620948624</v>
+        <v>-0.2029888770630244</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.04471976735636463</v>
+        <v>0.04337024057077432</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.04471976735636463</v>
+        <v>0.04337024057077432</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -7094,13 +7094,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5806390957080064</v>
+        <v>-0.5822916935685463</v>
       </c>
       <c r="O3" s="5">
         <v>68</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09146655366175763</v>
+        <v>0.09144260296812662</v>
       </c>
       <c r="Q3" s="4">
         <v>0.08398457123455133</v>
@@ -7153,16 +7153,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.641035162371842</v>
+        <v>-0.6067602015391174</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1236471364936624</v>
+        <v>0.1218557935345164</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1236471364936624</v>
+        <v>0.1218557935345164</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -7212,16 +7212,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.415760486259147</v>
+        <v>-0.4023412093592853</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.069624249625233</v>
+        <v>0.06872963116524224</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.069624249625233</v>
+        <v>0.06872963116524224</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -7271,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.045465534729373</v>
+        <v>-1.059592244884723</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
@@ -7330,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.7864290230645444</v>
+        <v>-0.7485456679096298</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
@@ -7389,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7612220096880336</v>
+        <v>-0.7456087221326371</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
@@ -8023,16 +8023,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0250426325175028</v>
+        <v>-0.02959660850684109</v>
       </c>
       <c r="O3" s="5">
         <v>68</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06038834871192938</v>
+        <v>0.0599303394635156</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05291422982109615</v>
+        <v>0.05251645537769596</v>
       </c>
       <c r="R3" s="5">
         <v>68</v>
@@ -8082,16 +8082,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3445565125105959</v>
+        <v>-0.3311097180558136</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1128108783085701</v>
+        <v>0.1124981621584589</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1128108783085701</v>
+        <v>0.1124981621584589</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -8141,16 +8141,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1051655530274723</v>
+        <v>-0.0919286087227964</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.03900533064734445</v>
+        <v>0.03704673268948877</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.03900533064734445</v>
+        <v>0.03704673268948877</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -8200,16 +8200,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.2621891258186365</v>
+        <v>-0.2718870529461439</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
       </c>
       <c r="P6" s="4">
-        <v>0.04456521639955575</v>
+        <v>0.04303211110588275</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.04456521639955575</v>
+        <v>0.04303211110588275</v>
       </c>
       <c r="R6" s="5">
         <v>12</v>
@@ -8259,16 +8259,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3736566320731165</v>
+        <v>-0.3442642728405296</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.08671287597220705</v>
+        <v>0.08336630946360317</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.08671287597220705</v>
+        <v>0.08336630946360317</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -8318,16 +8318,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2541580481001686</v>
+        <v>-0.23973865758669</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.04539758951410522</v>
+        <v>0.04416902476715112</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.04539758951410522</v>
+        <v>0.04416902476715112</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -8952,16 +8952,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7075362019174054</v>
+        <v>-0.7481247985196831</v>
       </c>
       <c r="O3" s="5">
         <v>67</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1827618505479273</v>
+        <v>0.177886667923032</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1758825892508664</v>
+        <v>0.1720734786849975</v>
       </c>
       <c r="R3" s="5">
         <v>67</v>
@@ -9011,16 +9011,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5602954729440921</v>
+        <v>-0.5409537385348813</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1427748122292286</v>
+        <v>0.1411923441758788</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1427748122292286</v>
+        <v>0.1411923441758788</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -9070,16 +9070,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2841275999288508</v>
+        <v>-0.2553942291924614</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07010117919888753</v>
+        <v>0.0681856211497949</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07010117919888753</v>
+        <v>0.0681856211497949</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -9129,16 +9129,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.9497386870807641</v>
+        <v>-0.9755908935003639</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1621786347595811</v>
+        <v>0.1609716737796812</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1621786347595811</v>
+        <v>0.1609716737796812</v>
       </c>
       <c r="R6" s="5">
         <v>12</v>
@@ -9188,7 +9188,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3708931943450067</v>
+        <v>-0.388554242850633</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
@@ -9247,16 +9247,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1877471042344059</v>
+        <v>-0.1266965112736074</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1159569599110548</v>
+        <v>0.1010357367695232</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1159569599110548</v>
+        <v>0.1010357367695232</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -9841,13 +9841,13 @@
         <v>1.176470588235294</v>
       </c>
       <c r="H3" s="4">
-        <v>0.5283140175516561</v>
+        <v>0.5268287938648427</v>
       </c>
       <c r="I3" s="4">
-        <v>0.191681481053005</v>
+        <v>0.1887962747878068</v>
       </c>
       <c r="J3" s="4">
-        <v>1.74660099816215</v>
+        <v>1.747329080277439</v>
       </c>
       <c r="K3" s="4">
         <v>85.63305322128812</v>
@@ -9891,13 +9891,13 @@
         <v>2.352941176470588</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3378767949563635</v>
+        <v>0.3305853722749281</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2762140044176204</v>
+        <v>0.2681765146653504</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3358141045954836</v>
+        <v>0.3325875135749811</v>
       </c>
       <c r="K4" s="4">
         <v>78.59343737494996</v>
@@ -9941,13 +9941,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2200104420116622</v>
+        <v>0.217388408858674</v>
       </c>
       <c r="I5" s="4">
-        <v>0.203806818738924</v>
+        <v>0.2017830458702826</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2176132007401296</v>
+        <v>0.2148436498477488</v>
       </c>
       <c r="K5" s="4">
         <v>85.18047218887553</v>
@@ -9991,13 +9991,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3120005846129263</v>
+        <v>0.3031850354624861</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3043247365525005</v>
+        <v>0.2963085477506648</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3265185133892496</v>
+        <v>0.3198459682157537</v>
       </c>
       <c r="K6" s="4">
         <v>85.76390556222483</v>
@@ -10041,13 +10041,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1872094179187212</v>
+        <v>0.1836055061849894</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1749350602625438</v>
+        <v>0.1716220439382552</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1848432368859315</v>
+        <v>0.1833282354136934</v>
       </c>
       <c r="K7" s="4">
         <v>87.31732693077231</v>
@@ -10091,13 +10091,13 @@
         <v>1.764705882352941</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3864604962746935</v>
+        <v>0.3691218007879414</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1976716265905121</v>
+        <v>0.1702394401118406</v>
       </c>
       <c r="J8" s="4">
-        <v>0.7206112021723876</v>
+        <v>0.7035581394406611</v>
       </c>
       <c r="K8" s="4">
         <v>83.50880352140895</v>
@@ -10141,13 +10141,13 @@
         <v>2.352941176470588</v>
       </c>
       <c r="H9" s="4">
-        <v>0.5143715170288179</v>
+        <v>0.5004428832511086</v>
       </c>
       <c r="I9" s="4">
-        <v>0.4399393750058248</v>
+        <v>0.4250281019409058</v>
       </c>
       <c r="J9" s="4">
-        <v>0.5015381579722077</v>
+        <v>0.4960854138633402</v>
       </c>
       <c r="K9" s="4">
         <v>84.05982392957198</v>
@@ -10191,13 +10191,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2233348624867556</v>
+        <v>0.2148207713667741</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2211669639138429</v>
+        <v>0.2127309576745738</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2142507787923709</v>
+        <v>0.2085822764123733</v>
       </c>
       <c r="K10" s="4">
         <v>83.71228491396552</v>
@@ -10241,13 +10241,13 @@
         <v>1.176470588235294</v>
       </c>
       <c r="H11" s="4">
-        <v>0.5663191554748203</v>
+        <v>0.5083052881253346</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2668821957233294</v>
+        <v>0.178191763614893</v>
       </c>
       <c r="J11" s="4">
-        <v>1.997971020731759</v>
+        <v>1.938102225917186</v>
       </c>
       <c r="K11" s="4">
         <v>81.90336134453773</v>
@@ -10291,13 +10291,13 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4993512082829646</v>
+        <v>0.465403160400092</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2302973476924355</v>
+        <v>0.1834800415039306</v>
       </c>
       <c r="J12" s="4">
-        <v>1.428375428924674</v>
+        <v>1.395540258530994</v>
       </c>
       <c r="K12" s="4">
         <v>84.22689075630211</v>
@@ -10341,13 +10341,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.08508335941305122</v>
+        <v>0.08380891187546942</v>
       </c>
       <c r="I13" s="4">
-        <v>0.07636948968961135</v>
+        <v>0.07516176170605125</v>
       </c>
       <c r="J13" s="4">
-        <v>0.07637192325441444</v>
+        <v>0.07614614857980978</v>
       </c>
       <c r="K13" s="4">
         <v>96.33633453381346</v>
@@ -10391,13 +10391,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1673750393297781</v>
+        <v>0.1668332768474035</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1521021649989123</v>
+        <v>0.1515637898552031</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1593719837529097</v>
+        <v>0.161128233434667</v>
       </c>
       <c r="K14" s="4">
         <v>81.65386154461778</v>
@@ -10441,13 +10441,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.08258520467171436</v>
+        <v>0.0817451283095607</v>
       </c>
       <c r="I15" s="4">
-        <v>0.07392715009064507</v>
+        <v>0.07310417981935469</v>
       </c>
       <c r="J15" s="4">
-        <v>0.07301577205589728</v>
+        <v>0.07299961066836703</v>
       </c>
       <c r="K15" s="4">
         <v>96.38775510204076</v>
@@ -10491,13 +10491,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1927555035451202</v>
+        <v>0.1894200893390069</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1750435465166964</v>
+        <v>0.1721167801201018</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1930334749830687</v>
+        <v>0.19168346626844</v>
       </c>
       <c r="K16" s="4">
         <v>82.6354541816727</v>
@@ -12106,16 +12106,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7858811850830664</v>
+        <v>-0.8020775091135874</v>
       </c>
       <c r="O3" s="5">
         <v>56</v>
       </c>
       <c r="P3" s="4">
-        <v>0.629049778937375</v>
+        <v>0.6307433840463447</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1296066603166885</v>
+        <v>0.1290904431067637</v>
       </c>
       <c r="R3" s="5">
         <v>56</v>
@@ -12165,16 +12165,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.509623079473918</v>
+        <v>-1.480879886643379</v>
       </c>
       <c r="O4" s="5">
         <v>41</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1721387995543739</v>
+        <v>0.1714535972364396</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1601132149515945</v>
+        <v>0.157992481163003</v>
       </c>
       <c r="R4" s="5">
         <v>41</v>
@@ -12224,16 +12224,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3820448401020258</v>
+        <v>-0.3546879767418432</v>
       </c>
       <c r="O5" s="5">
         <v>14</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07793361809647953</v>
+        <v>0.06952041016653918</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.076050727875554</v>
+        <v>0.06899063819063096</v>
       </c>
       <c r="R5" s="5">
         <v>14</v>
@@ -12283,16 +12283,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.914633704946836</v>
+        <v>-1.91037456059712</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8312716801891064</v>
+        <v>0.830561822797487</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.09297439989322699</v>
+        <v>0.09250116163214746</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -12342,16 +12342,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.823085662292821</v>
+        <v>-1.777399258568039</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1680379428499792</v>
+        <v>0.1609133811471111</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1680379428499792</v>
+        <v>0.1609133811471111</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -12401,16 +12401,16 @@
         <v>6</v>
       </c>
       <c r="N8" s="4">
-        <v>-2.071545867390341</v>
+        <v>-2.111163874367776</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1074046680109859</v>
+        <v>0.09244567657060543</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1074046680109859</v>
+        <v>0.09244567657060543</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -13027,16 +13027,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6422898540980467</v>
+        <v>-0.5764043545350432</v>
       </c>
       <c r="O3" s="5">
         <v>68</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2344513899840103</v>
+        <v>0.2296215173246046</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.234579309899937</v>
+        <v>0.2287095052960841</v>
       </c>
       <c r="R3" s="5">
         <v>68</v>
@@ -13086,16 +13086,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.42624582436129</v>
+        <v>-1.495162631101266</v>
       </c>
       <c r="O4" s="5">
         <v>39</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3194789606294099</v>
+        <v>0.3125976061124929</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3141857013003402</v>
+        <v>0.3065985668329701</v>
       </c>
       <c r="R4" s="5">
         <v>39</v>
@@ -13145,16 +13145,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4118040626957996</v>
+        <v>-0.3843375778997142</v>
       </c>
       <c r="O5" s="5">
         <v>14</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1401106776434019</v>
+        <v>0.1382795786569962</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1469821956821502</v>
+        <v>0.1469821956821501</v>
       </c>
       <c r="R5" s="5">
         <v>14</v>
@@ -13204,16 +13204,16 @@
         <v>9</v>
       </c>
       <c r="N6" s="4">
-        <v>-2.200337435605737</v>
+        <v>-2.142879995652038</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1822915155685728</v>
+        <v>0.1803353664066284</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1822915155685728</v>
+        <v>0.1803353664066284</v>
       </c>
       <c r="R6" s="5">
         <v>12</v>
@@ -13263,16 +13263,16 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.766933159597102</v>
+        <v>-1.907919252840657</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2637222038768717</v>
+        <v>0.2249582282044381</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2637222038768717</v>
+        <v>0.2249582282044381</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -13322,16 +13322,16 @@
         <v>2</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.883528975910849</v>
+        <v>-1.93321418560663</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1191616293347124</v>
+        <v>0.1073773274210907</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1191616293347124</v>
+        <v>0.1073773274210907</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -13940,16 +13940,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3192568480447363</v>
+        <v>-0.3558566279825754</v>
       </c>
       <c r="O3" s="5">
         <v>66</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1925348716188421</v>
+        <v>0.1885914294109988</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1782069973390644</v>
+        <v>0.1757479341189482</v>
       </c>
       <c r="R3" s="5">
         <v>66</v>
@@ -13999,16 +13999,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7561845771884099</v>
+        <v>-0.7830674946308136</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.175458686691695</v>
+        <v>0.1748335025651275</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.175458686691695</v>
+        <v>0.1748335025651275</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -14058,16 +14058,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2938191567203224</v>
+        <v>-0.2764528573025018</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07543946564029386</v>
+        <v>0.07183187581686071</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07543946564029386</v>
+        <v>0.07183187581686071</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -14117,7 +14117,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.9077436478710297</v>
+        <v>-0.8965492200914014</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
@@ -14176,16 +14176,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.9628617183043389</v>
+        <v>-0.9172748925957421</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1502210636232727</v>
+        <v>0.1446455172166073</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1502210636232727</v>
+        <v>0.1446455172166073</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -14235,16 +14235,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.022220986104912</v>
+        <v>-1.035754417858698</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1073706034351289</v>
+        <v>0.1041525031860147</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1073706034351289</v>
+        <v>0.1041525031860147</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -14869,16 +14869,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1067182180469183</v>
+        <v>-0.2252979474033054</v>
       </c>
       <c r="O3" s="5">
         <v>66</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3585496329870271</v>
+        <v>0.3416611479243737</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3417775019236617</v>
+        <v>0.3259180210150754</v>
       </c>
       <c r="R3" s="5">
         <v>66</v>
@@ -14928,16 +14928,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.9418283837281379</v>
+        <v>-0.9051159579685191</v>
       </c>
       <c r="O4" s="5">
         <v>39</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2016976120663701</v>
+        <v>0.197377426878564</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1902676805604414</v>
+        <v>0.1873870879564306</v>
       </c>
       <c r="R4" s="5">
         <v>39</v>
@@ -14987,16 +14987,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4066903262675624</v>
+        <v>-0.4283709293740685</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1129262763238512</v>
+        <v>0.1114809027834174</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1129262763238512</v>
+        <v>0.1114809027834174</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -15046,16 +15046,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.053482796552392</v>
+        <v>-1.000165421002748</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1665468338036994</v>
+        <v>0.1560560571312332</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1665468338036994</v>
+        <v>0.1560560571312332</v>
       </c>
       <c r="R6" s="5">
         <v>12</v>
@@ -15105,7 +15105,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.227590040929499</v>
+        <v>-1.222582086531474</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
@@ -15164,7 +15164,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.276683120197958</v>
+        <v>-1.255495388078998</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
@@ -15802,16 +15802,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08011871600607645</v>
+        <v>-0.1536831202538451</v>
       </c>
       <c r="O3" s="5">
         <v>67</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2359501698926169</v>
+        <v>0.228446023077529</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2298531890407995</v>
+        <v>0.2230609226924625</v>
       </c>
       <c r="R3" s="5">
         <v>67</v>
@@ -15861,16 +15861,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7575149057305426</v>
+        <v>-0.7466069708534633</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1013285760711793</v>
+        <v>0.1004515358128079</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1013285760711793</v>
+        <v>0.1004515358128079</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -15920,16 +15920,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2407621690969487</v>
+        <v>-0.2331243314692983</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.05709242101487084</v>
+        <v>0.05654189311947751</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.05709242101487084</v>
+        <v>0.05654189311947751</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -15979,7 +15979,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.7423204042540116</v>
+        <v>-0.7485282165107492</v>
       </c>
       <c r="O6" s="5">
         <v>12</v>
@@ -16038,16 +16038,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.8450120256020455</v>
+        <v>-0.8149796334655548</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1137857947530089</v>
+        <v>0.1103352846766938</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1137857947530089</v>
+        <v>0.1103352846766938</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -16097,16 +16097,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7981387657591767</v>
+        <v>-0.813859238736768</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.0459569714078043</v>
+        <v>0.04501920965321915</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.0459569714078043</v>
+        <v>0.04501920965321915</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
